--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-01T00:09:35+00:00</t>
+    <t>2024-11-02T14:29:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-02T14:29:07+00:00</t>
+    <t>2024-11-03T13:31:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T13:31:03+00:00</t>
+    <t>2024-11-05T09:51:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T09:51:29+00:00</t>
+    <t>2024-11-05T12:11:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T12:11:21+00:00</t>
+    <t>2024-11-05T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/fix-tx-error/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T13:22:43+00:00</t>
+    <t>2024-11-06T02:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
